--- a/P012-excavator-split_data_files/17_05_2017_cherinet_bisetegn _excavator_records_part_5.xlsx
+++ b/P012-excavator-split_data_files/17_05_2017_cherinet_bisetegn _excavator_records_part_5.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="excavator" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="mpdm" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="daily_variables" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="excavator" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mpdm" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_variables" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z32"/>
+  <dimension ref="A1:Z111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.875" customWidth="1" min="1" max="1"/>
@@ -3108,6 +3108,3403 @@
       <c r="X32" s="10" t="n"/>
       <c r="Y32" s="10" t="n"/>
       <c r="Z32" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="E33" t="n">
+        <v>405</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>90</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="E34" t="n">
+        <v>405</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>90</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R34" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="E35" t="n">
+        <v>405</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>90</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R35" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="E36" t="n">
+        <v>405</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>90</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R36" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="E37" t="n">
+        <v>405</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>90</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R37" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="E38" t="n">
+        <v>405</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>90</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R38" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="E39" t="n">
+        <v>405</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>90</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R39" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="E40" t="n">
+        <v>405</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>90</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R40" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="E41" t="n">
+        <v>405</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>90</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R41" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="E42" t="n">
+        <v>405</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>90</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R42" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="E43" t="n">
+        <v>405</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>90</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R43" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="E44" t="n">
+        <v>405</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>90</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R44" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="E45" t="n">
+        <v>405</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>90</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R45" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="E46" t="n">
+        <v>405</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>90</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R46" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="E47" t="n">
+        <v>405</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>90</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R47" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="E48" t="n">
+        <v>405</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>90</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R48" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="E49" t="n">
+        <v>405</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="n">
+        <v>90</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R49" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="E50" t="n">
+        <v>405</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>90</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R50" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="E51" t="n">
+        <v>405</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" t="n">
+        <v>90</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R51" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="E52" t="n">
+        <v>405</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>90</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R52" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="E53" t="n">
+        <v>405</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>90</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R53" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="E54" t="n">
+        <v>405</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>90</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R54" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="E55" t="n">
+        <v>405</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" t="n">
+        <v>90</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R55" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="E56" t="n">
+        <v>405</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" t="n">
+        <v>90</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R56" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="E57" t="n">
+        <v>405</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>90</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R57" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="E58" t="n">
+        <v>405</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" t="n">
+        <v>90</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R58" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="E59" t="n">
+        <v>405</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" t="n">
+        <v>90</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R59" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="E60" t="n">
+        <v>405</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" t="n">
+        <v>90</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R60" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="E61" t="n">
+        <v>405</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" t="n">
+        <v>90</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R61" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="E62" t="n">
+        <v>405</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" t="n">
+        <v>90</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R62" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="E63" t="n">
+        <v>405</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" t="n">
+        <v>90</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R63" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="E64" t="n">
+        <v>405</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" t="n">
+        <v>90</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R64" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="E65" t="n">
+        <v>405</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" t="n">
+        <v>90</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R65" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="E66" t="n">
+        <v>405</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>1</v>
+      </c>
+      <c r="L66" t="n">
+        <v>90</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R66" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="E67" t="n">
+        <v>405</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" t="n">
+        <v>90</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R67" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="E68" t="n">
+        <v>405</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" t="n">
+        <v>90</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R68" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="E69" t="n">
+        <v>405</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L69" t="n">
+        <v>90</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R69" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="E70" t="n">
+        <v>405</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" t="n">
+        <v>90</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R70" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="E71" t="n">
+        <v>405</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" t="n">
+        <v>90</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R71" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="E72" t="n">
+        <v>405</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" t="n">
+        <v>90</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R72" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="E73" t="n">
+        <v>405</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" t="n">
+        <v>90</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R73" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="E74" t="n">
+        <v>405</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" t="n">
+        <v>90</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R74" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="E75" t="n">
+        <v>405</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" t="n">
+        <v>90</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R75" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="E76" t="n">
+        <v>405</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" t="n">
+        <v>90</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R76" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="E77" t="n">
+        <v>405</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" t="n">
+        <v>90</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R77" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="E78" t="n">
+        <v>405</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" t="n">
+        <v>90</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R78" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="E79" t="n">
+        <v>405</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" t="n">
+        <v>90</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R79" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="E80" t="n">
+        <v>405</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" t="n">
+        <v>90</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R80" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="E81" t="n">
+        <v>405</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" t="n">
+        <v>90</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R81" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="E82" t="n">
+        <v>405</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" t="n">
+        <v>90</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R82" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="E83" t="n">
+        <v>405</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" t="n">
+        <v>90</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R83" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="E84" t="n">
+        <v>405</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" t="n">
+        <v>90</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R84" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="E85" t="n">
+        <v>405</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" t="n">
+        <v>90</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R85" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="E86" t="n">
+        <v>405</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" t="n">
+        <v>90</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R86" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="E87" t="n">
+        <v>405</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" t="n">
+        <v>90</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R87" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="E88" t="n">
+        <v>405</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" t="n">
+        <v>90</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R88" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="E89" t="n">
+        <v>405</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" t="n">
+        <v>90</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R89" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="E90" t="n">
+        <v>405</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" t="n">
+        <v>90</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R90" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="E91" t="n">
+        <v>405</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" t="n">
+        <v>90</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R91" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="E92" t="n">
+        <v>405</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" t="n">
+        <v>90</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R92" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="E93" t="n">
+        <v>405</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" t="n">
+        <v>90</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R93" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="E94" t="n">
+        <v>405</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" t="n">
+        <v>90</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R94" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="E95" t="n">
+        <v>405</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" t="n">
+        <v>90</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R95" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="E96" t="n">
+        <v>405</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" t="n">
+        <v>90</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R96" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="E97" t="n">
+        <v>405</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" t="n">
+        <v>90</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R97" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="E98" t="n">
+        <v>405</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" t="n">
+        <v>90</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R98" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="E99" t="n">
+        <v>405</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>1</v>
+      </c>
+      <c r="L99" t="n">
+        <v>90</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R99" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="E100" t="n">
+        <v>405</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" t="n">
+        <v>90</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R100" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="E101" t="n">
+        <v>405</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" t="n">
+        <v>90</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R101" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="E102" t="n">
+        <v>405</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>1</v>
+      </c>
+      <c r="L102" t="n">
+        <v>90</v>
+      </c>
+      <c r="M102" t="n">
+        <v>1</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R102" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="E103" t="n">
+        <v>405</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>1</v>
+      </c>
+      <c r="L103" t="n">
+        <v>90</v>
+      </c>
+      <c r="M103" t="n">
+        <v>1</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R103" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="E104" t="n">
+        <v>405</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>1</v>
+      </c>
+      <c r="L104" t="n">
+        <v>90</v>
+      </c>
+      <c r="M104" t="n">
+        <v>1</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R104" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="E105" t="n">
+        <v>405</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>1</v>
+      </c>
+      <c r="L105" t="n">
+        <v>90</v>
+      </c>
+      <c r="M105" t="n">
+        <v>1</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R105" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="E106" t="n">
+        <v>405</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>1</v>
+      </c>
+      <c r="L106" t="n">
+        <v>90</v>
+      </c>
+      <c r="M106" t="n">
+        <v>1</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R106" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="E107" t="n">
+        <v>405</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>1</v>
+      </c>
+      <c r="L107" t="n">
+        <v>90</v>
+      </c>
+      <c r="M107" t="n">
+        <v>1</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R107" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="E108" t="n">
+        <v>405</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>1</v>
+      </c>
+      <c r="L108" t="n">
+        <v>90</v>
+      </c>
+      <c r="M108" t="n">
+        <v>1</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R108" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="E109" t="n">
+        <v>405</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" t="n">
+        <v>90</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R109" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="E110" t="n">
+        <v>405</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L110" t="n">
+        <v>90</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R110" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="E111" t="n">
+        <v>405</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>1</v>
+      </c>
+      <c r="L111" t="n">
+        <v>90</v>
+      </c>
+      <c r="M111" t="n">
+        <v>1</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R111" t="n">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -5307,7 +8704,7 @@
       </c>
       <c r="H21" s="69" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I21" s="67" t="n"/>

--- a/P012-excavator-split_data_files/17_05_2017_cherinet_bisetegn _excavator_records_part_5.xlsx
+++ b/P012-excavator-split_data_files/17_05_2017_cherinet_bisetegn _excavator_records_part_5.xlsx
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z111"/>
+  <dimension ref="A1:Z32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.875" customWidth="1" min="1" max="1"/>
@@ -1628,10 +1628,22 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n"/>
-      <c r="B7" s="18" t="n"/>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="18" t="n"/>
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>17-05-2017</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Cherinet Bisetegn</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>2</v>
+      </c>
       <c r="E7" s="19" t="n">
         <v>401</v>
       </c>
@@ -3108,3403 +3120,6 @@
       <c r="X32" s="10" t="n"/>
       <c r="Y32" s="10" t="n"/>
       <c r="Z32" s="10" t="n"/>
-    </row>
-    <row r="33">
-      <c r="E33" t="n">
-        <v>405</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="n">
-        <v>90</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R33" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="E34" t="n">
-        <v>405</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="n">
-        <v>90</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R34" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="E35" t="n">
-        <v>405</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>90</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R35" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="E36" t="n">
-        <v>405</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="n">
-        <v>90</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R36" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="E37" t="n">
-        <v>405</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" t="n">
-        <v>90</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R37" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="E38" t="n">
-        <v>405</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" t="n">
-        <v>90</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R38" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="E39" t="n">
-        <v>405</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" t="n">
-        <v>90</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R39" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="E40" t="n">
-        <v>405</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" t="n">
-        <v>90</v>
-      </c>
-      <c r="M40" t="n">
-        <v>1</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R40" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="E41" t="n">
-        <v>405</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K41" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" t="n">
-        <v>90</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R41" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="E42" t="n">
-        <v>405</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" t="n">
-        <v>90</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R42" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="E43" t="n">
-        <v>405</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K43" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" t="n">
-        <v>90</v>
-      </c>
-      <c r="M43" t="n">
-        <v>1</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R43" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="E44" t="n">
-        <v>405</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K44" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" t="n">
-        <v>90</v>
-      </c>
-      <c r="M44" t="n">
-        <v>1</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R44" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="E45" t="n">
-        <v>405</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
-        <v>90</v>
-      </c>
-      <c r="M45" t="n">
-        <v>1</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R45" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="E46" t="n">
-        <v>405</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" t="n">
-        <v>90</v>
-      </c>
-      <c r="M46" t="n">
-        <v>1</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R46" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="E47" t="n">
-        <v>405</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K47" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" t="n">
-        <v>90</v>
-      </c>
-      <c r="M47" t="n">
-        <v>1</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R47" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="E48" t="n">
-        <v>405</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K48" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" t="n">
-        <v>90</v>
-      </c>
-      <c r="M48" t="n">
-        <v>1</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R48" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="E49" t="n">
-        <v>405</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" t="n">
-        <v>90</v>
-      </c>
-      <c r="M49" t="n">
-        <v>1</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R49" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="E50" t="n">
-        <v>405</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" t="n">
-        <v>90</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R50" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="E51" t="n">
-        <v>405</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" t="n">
-        <v>90</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R51" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="E52" t="n">
-        <v>405</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
-        <v>1</v>
-      </c>
-      <c r="L52" t="n">
-        <v>90</v>
-      </c>
-      <c r="M52" t="n">
-        <v>1</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R52" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="E53" t="n">
-        <v>405</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" t="n">
-        <v>90</v>
-      </c>
-      <c r="M53" t="n">
-        <v>1</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R53" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="E54" t="n">
-        <v>405</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
-        <v>1</v>
-      </c>
-      <c r="L54" t="n">
-        <v>90</v>
-      </c>
-      <c r="M54" t="n">
-        <v>1</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R54" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="E55" t="n">
-        <v>405</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" t="n">
-        <v>90</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R55" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="E56" t="n">
-        <v>405</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K56" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" t="n">
-        <v>90</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R56" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="E57" t="n">
-        <v>405</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
-        <v>1</v>
-      </c>
-      <c r="L57" t="n">
-        <v>90</v>
-      </c>
-      <c r="M57" t="n">
-        <v>1</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R57" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="E58" t="n">
-        <v>405</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K58" t="n">
-        <v>1</v>
-      </c>
-      <c r="L58" t="n">
-        <v>90</v>
-      </c>
-      <c r="M58" t="n">
-        <v>1</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R58" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="E59" t="n">
-        <v>405</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
-        <v>1</v>
-      </c>
-      <c r="L59" t="n">
-        <v>90</v>
-      </c>
-      <c r="M59" t="n">
-        <v>1</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R59" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="E60" t="n">
-        <v>405</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K60" t="n">
-        <v>1</v>
-      </c>
-      <c r="L60" t="n">
-        <v>90</v>
-      </c>
-      <c r="M60" t="n">
-        <v>1</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R60" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="E61" t="n">
-        <v>405</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K61" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" t="n">
-        <v>90</v>
-      </c>
-      <c r="M61" t="n">
-        <v>1</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R61" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="E62" t="n">
-        <v>405</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K62" t="n">
-        <v>1</v>
-      </c>
-      <c r="L62" t="n">
-        <v>90</v>
-      </c>
-      <c r="M62" t="n">
-        <v>1</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R62" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="E63" t="n">
-        <v>405</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K63" t="n">
-        <v>1</v>
-      </c>
-      <c r="L63" t="n">
-        <v>90</v>
-      </c>
-      <c r="M63" t="n">
-        <v>1</v>
-      </c>
-      <c r="N63" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R63" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="E64" t="n">
-        <v>405</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K64" t="n">
-        <v>1</v>
-      </c>
-      <c r="L64" t="n">
-        <v>90</v>
-      </c>
-      <c r="M64" t="n">
-        <v>1</v>
-      </c>
-      <c r="N64" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R64" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="E65" t="n">
-        <v>405</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K65" t="n">
-        <v>1</v>
-      </c>
-      <c r="L65" t="n">
-        <v>90</v>
-      </c>
-      <c r="M65" t="n">
-        <v>1</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R65" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="E66" t="n">
-        <v>405</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K66" t="n">
-        <v>1</v>
-      </c>
-      <c r="L66" t="n">
-        <v>90</v>
-      </c>
-      <c r="M66" t="n">
-        <v>1</v>
-      </c>
-      <c r="N66" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R66" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="E67" t="n">
-        <v>405</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K67" t="n">
-        <v>1</v>
-      </c>
-      <c r="L67" t="n">
-        <v>90</v>
-      </c>
-      <c r="M67" t="n">
-        <v>1</v>
-      </c>
-      <c r="N67" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R67" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="E68" t="n">
-        <v>405</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K68" t="n">
-        <v>1</v>
-      </c>
-      <c r="L68" t="n">
-        <v>90</v>
-      </c>
-      <c r="M68" t="n">
-        <v>1</v>
-      </c>
-      <c r="N68" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R68" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="E69" t="n">
-        <v>405</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K69" t="n">
-        <v>1</v>
-      </c>
-      <c r="L69" t="n">
-        <v>90</v>
-      </c>
-      <c r="M69" t="n">
-        <v>1</v>
-      </c>
-      <c r="N69" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R69" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="E70" t="n">
-        <v>405</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K70" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" t="n">
-        <v>90</v>
-      </c>
-      <c r="M70" t="n">
-        <v>1</v>
-      </c>
-      <c r="N70" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R70" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="E71" t="n">
-        <v>405</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K71" t="n">
-        <v>1</v>
-      </c>
-      <c r="L71" t="n">
-        <v>90</v>
-      </c>
-      <c r="M71" t="n">
-        <v>1</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R71" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="E72" t="n">
-        <v>405</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K72" t="n">
-        <v>1</v>
-      </c>
-      <c r="L72" t="n">
-        <v>90</v>
-      </c>
-      <c r="M72" t="n">
-        <v>1</v>
-      </c>
-      <c r="N72" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R72" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="E73" t="n">
-        <v>405</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K73" t="n">
-        <v>1</v>
-      </c>
-      <c r="L73" t="n">
-        <v>90</v>
-      </c>
-      <c r="M73" t="n">
-        <v>1</v>
-      </c>
-      <c r="N73" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R73" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="E74" t="n">
-        <v>405</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K74" t="n">
-        <v>1</v>
-      </c>
-      <c r="L74" t="n">
-        <v>90</v>
-      </c>
-      <c r="M74" t="n">
-        <v>1</v>
-      </c>
-      <c r="N74" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R74" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="E75" t="n">
-        <v>405</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K75" t="n">
-        <v>1</v>
-      </c>
-      <c r="L75" t="n">
-        <v>90</v>
-      </c>
-      <c r="M75" t="n">
-        <v>1</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R75" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="E76" t="n">
-        <v>405</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K76" t="n">
-        <v>1</v>
-      </c>
-      <c r="L76" t="n">
-        <v>90</v>
-      </c>
-      <c r="M76" t="n">
-        <v>1</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R76" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="E77" t="n">
-        <v>405</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K77" t="n">
-        <v>1</v>
-      </c>
-      <c r="L77" t="n">
-        <v>90</v>
-      </c>
-      <c r="M77" t="n">
-        <v>1</v>
-      </c>
-      <c r="N77" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R77" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="E78" t="n">
-        <v>405</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K78" t="n">
-        <v>1</v>
-      </c>
-      <c r="L78" t="n">
-        <v>90</v>
-      </c>
-      <c r="M78" t="n">
-        <v>1</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R78" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="E79" t="n">
-        <v>405</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K79" t="n">
-        <v>1</v>
-      </c>
-      <c r="L79" t="n">
-        <v>90</v>
-      </c>
-      <c r="M79" t="n">
-        <v>1</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R79" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="E80" t="n">
-        <v>405</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K80" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" t="n">
-        <v>90</v>
-      </c>
-      <c r="M80" t="n">
-        <v>1</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R80" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="E81" t="n">
-        <v>405</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K81" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" t="n">
-        <v>90</v>
-      </c>
-      <c r="M81" t="n">
-        <v>1</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R81" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="E82" t="n">
-        <v>405</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K82" t="n">
-        <v>1</v>
-      </c>
-      <c r="L82" t="n">
-        <v>90</v>
-      </c>
-      <c r="M82" t="n">
-        <v>1</v>
-      </c>
-      <c r="N82" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R82" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="E83" t="n">
-        <v>405</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K83" t="n">
-        <v>1</v>
-      </c>
-      <c r="L83" t="n">
-        <v>90</v>
-      </c>
-      <c r="M83" t="n">
-        <v>1</v>
-      </c>
-      <c r="N83" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R83" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="E84" t="n">
-        <v>405</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K84" t="n">
-        <v>1</v>
-      </c>
-      <c r="L84" t="n">
-        <v>90</v>
-      </c>
-      <c r="M84" t="n">
-        <v>1</v>
-      </c>
-      <c r="N84" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R84" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="E85" t="n">
-        <v>405</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K85" t="n">
-        <v>1</v>
-      </c>
-      <c r="L85" t="n">
-        <v>90</v>
-      </c>
-      <c r="M85" t="n">
-        <v>1</v>
-      </c>
-      <c r="N85" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R85" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="E86" t="n">
-        <v>405</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K86" t="n">
-        <v>1</v>
-      </c>
-      <c r="L86" t="n">
-        <v>90</v>
-      </c>
-      <c r="M86" t="n">
-        <v>1</v>
-      </c>
-      <c r="N86" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R86" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="E87" t="n">
-        <v>405</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K87" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" t="n">
-        <v>90</v>
-      </c>
-      <c r="M87" t="n">
-        <v>1</v>
-      </c>
-      <c r="N87" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R87" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="E88" t="n">
-        <v>405</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K88" t="n">
-        <v>1</v>
-      </c>
-      <c r="L88" t="n">
-        <v>90</v>
-      </c>
-      <c r="M88" t="n">
-        <v>1</v>
-      </c>
-      <c r="N88" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R88" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="E89" t="n">
-        <v>405</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K89" t="n">
-        <v>1</v>
-      </c>
-      <c r="L89" t="n">
-        <v>90</v>
-      </c>
-      <c r="M89" t="n">
-        <v>1</v>
-      </c>
-      <c r="N89" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R89" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="E90" t="n">
-        <v>405</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K90" t="n">
-        <v>1</v>
-      </c>
-      <c r="L90" t="n">
-        <v>90</v>
-      </c>
-      <c r="M90" t="n">
-        <v>1</v>
-      </c>
-      <c r="N90" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R90" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="E91" t="n">
-        <v>405</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K91" t="n">
-        <v>1</v>
-      </c>
-      <c r="L91" t="n">
-        <v>90</v>
-      </c>
-      <c r="M91" t="n">
-        <v>1</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R91" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="E92" t="n">
-        <v>405</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K92" t="n">
-        <v>1</v>
-      </c>
-      <c r="L92" t="n">
-        <v>90</v>
-      </c>
-      <c r="M92" t="n">
-        <v>1</v>
-      </c>
-      <c r="N92" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R92" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="E93" t="n">
-        <v>405</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K93" t="n">
-        <v>1</v>
-      </c>
-      <c r="L93" t="n">
-        <v>90</v>
-      </c>
-      <c r="M93" t="n">
-        <v>1</v>
-      </c>
-      <c r="N93" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R93" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="E94" t="n">
-        <v>405</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K94" t="n">
-        <v>1</v>
-      </c>
-      <c r="L94" t="n">
-        <v>90</v>
-      </c>
-      <c r="M94" t="n">
-        <v>1</v>
-      </c>
-      <c r="N94" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R94" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="E95" t="n">
-        <v>405</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K95" t="n">
-        <v>1</v>
-      </c>
-      <c r="L95" t="n">
-        <v>90</v>
-      </c>
-      <c r="M95" t="n">
-        <v>1</v>
-      </c>
-      <c r="N95" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R95" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="E96" t="n">
-        <v>405</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K96" t="n">
-        <v>1</v>
-      </c>
-      <c r="L96" t="n">
-        <v>90</v>
-      </c>
-      <c r="M96" t="n">
-        <v>1</v>
-      </c>
-      <c r="N96" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R96" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="E97" t="n">
-        <v>405</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K97" t="n">
-        <v>1</v>
-      </c>
-      <c r="L97" t="n">
-        <v>90</v>
-      </c>
-      <c r="M97" t="n">
-        <v>1</v>
-      </c>
-      <c r="N97" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R97" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="E98" t="n">
-        <v>405</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K98" t="n">
-        <v>1</v>
-      </c>
-      <c r="L98" t="n">
-        <v>90</v>
-      </c>
-      <c r="M98" t="n">
-        <v>1</v>
-      </c>
-      <c r="N98" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R98" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="E99" t="n">
-        <v>405</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K99" t="n">
-        <v>1</v>
-      </c>
-      <c r="L99" t="n">
-        <v>90</v>
-      </c>
-      <c r="M99" t="n">
-        <v>1</v>
-      </c>
-      <c r="N99" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R99" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="E100" t="n">
-        <v>405</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K100" t="n">
-        <v>1</v>
-      </c>
-      <c r="L100" t="n">
-        <v>90</v>
-      </c>
-      <c r="M100" t="n">
-        <v>1</v>
-      </c>
-      <c r="N100" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R100" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="E101" t="n">
-        <v>405</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K101" t="n">
-        <v>1</v>
-      </c>
-      <c r="L101" t="n">
-        <v>90</v>
-      </c>
-      <c r="M101" t="n">
-        <v>1</v>
-      </c>
-      <c r="N101" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R101" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="E102" t="n">
-        <v>405</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K102" t="n">
-        <v>1</v>
-      </c>
-      <c r="L102" t="n">
-        <v>90</v>
-      </c>
-      <c r="M102" t="n">
-        <v>1</v>
-      </c>
-      <c r="N102" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R102" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="E103" t="n">
-        <v>405</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K103" t="n">
-        <v>1</v>
-      </c>
-      <c r="L103" t="n">
-        <v>90</v>
-      </c>
-      <c r="M103" t="n">
-        <v>1</v>
-      </c>
-      <c r="N103" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R103" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="E104" t="n">
-        <v>405</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K104" t="n">
-        <v>1</v>
-      </c>
-      <c r="L104" t="n">
-        <v>90</v>
-      </c>
-      <c r="M104" t="n">
-        <v>1</v>
-      </c>
-      <c r="N104" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R104" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="E105" t="n">
-        <v>405</v>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K105" t="n">
-        <v>1</v>
-      </c>
-      <c r="L105" t="n">
-        <v>90</v>
-      </c>
-      <c r="M105" t="n">
-        <v>1</v>
-      </c>
-      <c r="N105" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R105" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="E106" t="n">
-        <v>405</v>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K106" t="n">
-        <v>1</v>
-      </c>
-      <c r="L106" t="n">
-        <v>90</v>
-      </c>
-      <c r="M106" t="n">
-        <v>1</v>
-      </c>
-      <c r="N106" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R106" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="E107" t="n">
-        <v>405</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K107" t="n">
-        <v>1</v>
-      </c>
-      <c r="L107" t="n">
-        <v>90</v>
-      </c>
-      <c r="M107" t="n">
-        <v>1</v>
-      </c>
-      <c r="N107" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R107" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="E108" t="n">
-        <v>405</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K108" t="n">
-        <v>1</v>
-      </c>
-      <c r="L108" t="n">
-        <v>90</v>
-      </c>
-      <c r="M108" t="n">
-        <v>1</v>
-      </c>
-      <c r="N108" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R108" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="E109" t="n">
-        <v>405</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K109" t="n">
-        <v>1</v>
-      </c>
-      <c r="L109" t="n">
-        <v>90</v>
-      </c>
-      <c r="M109" t="n">
-        <v>1</v>
-      </c>
-      <c r="N109" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R109" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="E110" t="n">
-        <v>405</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K110" t="n">
-        <v>1</v>
-      </c>
-      <c r="L110" t="n">
-        <v>90</v>
-      </c>
-      <c r="M110" t="n">
-        <v>1</v>
-      </c>
-      <c r="N110" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R110" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="E111" t="n">
-        <v>405</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K111" t="n">
-        <v>1</v>
-      </c>
-      <c r="L111" t="n">
-        <v>90</v>
-      </c>
-      <c r="M111" t="n">
-        <v>1</v>
-      </c>
-      <c r="N111" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R111" t="n">
-        <v>26</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -6914,7 +3529,7 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>17_05_2017</t>
+          <t>17-05-2017</t>
         </is>
       </c>
       <c r="B7" s="29" t="n">
